--- a/excel_routes/route_YNB_CCE_threats.xlsx
+++ b/excel_routes/route_YNB_CCE_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -532,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>971</v>
+        <v>863</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1148</v>
+        <v>1050</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-177</v>
+        <v>-187</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,12 +586,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -591,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>971</v>
+        <v>621</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1148</v>
+        <v>1050</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-177</v>
+        <v>-429</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,12 +631,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-442</t>
+          <t>SM-448</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -636,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>863</v>
+        <v>571</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1148</v>
+        <v>690</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-285</v>
+        <v>-119</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>863</v>
+        <v>571</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1148</v>
+        <v>600</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-285</v>
+        <v>-29</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,22 +735,22 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>621</v>
+        <v>571</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>788</v>
+        <v>690</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-167</v>
+        <v>-119</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,12 +766,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-442</t>
+          <t>SM-448</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -771,26 +780,26 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>621</v>
+        <v>571</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>788</v>
+        <v>810</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-167</v>
+        <v>-239</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,10 +825,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1101</v>
+        <v>763</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1148</v>
+        <v>810</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>-47</v>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -861,10 +870,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1101</v>
+        <v>763</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1148</v>
+        <v>810</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>-47</v>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -906,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1271</v>
+        <v>971</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1358</v>
+        <v>1170</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-87</v>
+        <v>-199</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1271</v>
+        <v>1101</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1358</v>
+        <v>1170</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-87</v>
+        <v>-69</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,12 +991,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -996,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2071</v>
+        <v>571</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2318</v>
+        <v>600</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-247</v>
+        <v>-29</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1013,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,12 +1036,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1041,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2071</v>
+        <v>571</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2318</v>
+        <v>600</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-247</v>
+        <v>-29</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1058,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2071</v>
+        <v>571</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2318</v>
+        <v>600</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-247</v>
+        <v>-29</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1103,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2071</v>
+        <v>571</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2318</v>
+        <v>600</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-247</v>
+        <v>-29</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1148,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2071</v>
+        <v>571</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2318</v>
+        <v>600</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-247</v>
+        <v>-29</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1193,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1221,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2071</v>
+        <v>571</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2318</v>
+        <v>600</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-247</v>
+        <v>-29</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1238,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1266,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>763</v>
+        <v>571</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>908</v>
+        <v>600</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-145</v>
+        <v>-29</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1311,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>763</v>
+        <v>571</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>908</v>
+        <v>600</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-145</v>
+        <v>-29</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1342,12 +1351,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1356,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>763</v>
+        <v>571</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>908</v>
+        <v>1050</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-145</v>
+        <v>-479</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1373,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,12 +1396,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1401,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>763</v>
+        <v>571</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>908</v>
+        <v>1050</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-145</v>
+        <v>-479</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1418,372 +1427,12 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16-JUN-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16-JUN-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-448</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>20-JUN-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-448</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>23-JUN-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>23-JUN-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>30-JUN-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>971</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1148</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-177</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>30-JUN-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>971</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1148</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-177</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_YNB_CCE_threats.xlsx
+++ b/excel_routes/route_YNB_CCE_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -558,10 +558,10 @@
         <v>863</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1050</v>
+        <v>930</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-187</v>
+        <v>-67</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>621</v>
+        <v>763</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1050</v>
+        <v>930</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-429</v>
+        <v>-167</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -648,10 +648,10 @@
         <v>571</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>690</v>
+        <v>810</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-119</v>
+        <v>-239</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-442</t>
+          <t>SM-448</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>571</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-29</v>
+        <v>-119</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>971</v>
+        <v>1271</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1170</v>
+        <v>1380</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-199</v>
+        <v>-109</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1101</v>
+        <v>971</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1170</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-69</v>
+        <v>-199</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>571</v>
+        <v>1101</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>600</v>
+        <v>1170</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-29</v>
+        <v>-69</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>571</v>
+        <v>671</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-29</v>
+        <v>-19</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1368,10 +1368,10 @@
         <v>571</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1050</v>
+        <v>600</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-479</v>
+        <v>-29</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1413,26 +1413,116 @@
         <v>571</v>
       </c>
       <c r="E21" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-29</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-442</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-104</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>1050</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F22" s="2" t="n">
         <v>-479</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-442</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-104</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-479</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
